--- a/TFT_prediction_remedy_plan/Iteration_3/Festive_Dates_for_plotting.xlsx
+++ b/TFT_prediction_remedy_plan/Iteration_3/Festive_Dates_for_plotting.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a1c0b903b3414e4/Desktop/Learning - post job/Time Series Forecasting/TFT - Study/Daily Sales Forecasting Methodology/Iteration 3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\G0004878\Desktop\TFT_Data\Temporal-Fusion-Transformers-Material\TFT_prediction_remedy_plan\Iteration_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A689F989-1608-40A6-8B2E-0572ECD438B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{CE69B548-6EBB-4427-8150-BF6170E86BE5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,7 +56,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -446,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F2922F5-D3FE-4130-9511-F59F0C66E5A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
